--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samiaomer/Documents/DataAnalytics/pre-week-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADC8EF9-06DD-6844-87A0-50E3B238AB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4493DB3D-918E-C145-9CE2-39988B8B6A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1320" windowWidth="27640" windowHeight="16880" xr2:uid="{84D7F0E5-C2C5-5E49-8C12-9F7417A06E5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">Store </t>
   </si>
@@ -78,19 +79,37 @@
   </si>
   <si>
     <t xml:space="preserve">Monthely Sales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student C </t>
+  </si>
+  <si>
+    <t>Studen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,8 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,7 +516,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -507,10 +527,7 @@
         <f>_xlfn.MODE.SNGL(B2:B13)</f>
         <v>46</v>
       </c>
-      <c r="D4">
-        <f>_xlfn.MODE.SNGL(B2:B8, B10:B13)</f>
-        <v>46</v>
-      </c>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -598,6 +615,36 @@
       </c>
       <c r="B13">
         <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B38636-4A65-6642-B211-67F84B0B4FFA}">
+  <dimension ref="A2:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
